--- a/ig/DM-JUILLET-2026/ValueSet-jdv-j419-perimetre-interruption-exercice-rpps.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-jdv-j419-perimetre-interruption-exercice-rpps.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.6.1.402</t>
+    <t>OID:1.2.250.1.213.1.6.1.403</t>
   </si>
   <si>
     <t>Version</t>
@@ -99,13 +99,19 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>=</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Permanente</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Temporaire</t>
   </si>
   <si>
     <t/>
@@ -378,7 +384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -387,13 +393,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
@@ -403,24 +406,29 @@
       <c r="B2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>13</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
